--- a/public/data/services.xlsx
+++ b/public/data/services.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\seva-setu-ui\seva-setu-ui\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3C921C58-28D5-4B13-AAFF-B8873B72BAC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E230EA31-157B-40E6-9873-FA6BFFC68FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35640" yWindow="3345" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34620" yWindow="3345" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
